--- a/tools/_out/groupB_20261021/stage/04_DESIGN_TABLES/DesignTable_6835.xlsx
+++ b/tools/_out/groupB_20261021/stage/04_DESIGN_TABLES/DesignTable_6835.xlsx
@@ -413,43 +413,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>OMi 6835 - Design Table SKELETON (no dimensional source) | OMi catalog 4 SKUs | ALL MISSING | GENERATED 2026-09-23</t>
+          <t>OMi 6835 - review table | Brennan TFA catalog TFA-p061-t02 + Brennan CAD records (group B 2026-10-21); port drill = Air-Way per-size (A11) | was a skeleton</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
+          <t>M7@DRIVE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>M1@DRIVE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>M2@DRIVE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>D1@BORE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CHEX@HEX</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Y@HEX</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PD2@BORE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>PD3@BORE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>THDMAJ_B1@DRIVE</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>$PRP@PartNo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>$PRP@DataStatus</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>$PRP@AxialSource</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>$PRP@ScopeAction</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>$COMMENT</t>
         </is>
@@ -461,32 +511,64 @@
           <t>6835-04-04-04-NWO-FG</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>6835-04-04-04-NWO-FG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAT 2026-10-21: M7@DRIVE, M1@DRIVE, M2@DRIVE, D1@BORE, CHEX@HEX, Y@HEX] Brennan TFA catalog TFA-p061-t02 (CAD record agrees within the print rounding); port drill PD2@BORE, PD3@BORE = Air-Way per-size (A11) [user 2026-10-18 "Brennan = yes"; 2026-10-21 CAD records "following my rule"]</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>6835-04-04-04-NWO-FG</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
         </is>
@@ -498,32 +580,64 @@
           <t>6835-06-06-06-NWO-FG</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>6835-06-06-06-NWO-FG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAT 2026-10-21: M7@DRIVE, M1@DRIVE, M2@DRIVE, D1@BORE, CHEX@HEX, Y@HEX] Brennan TFA catalog TFA-p061-t02 (CAD record agrees within the print rounding); port drill PD2@BORE, PD3@BORE = Air-Way per-size (A11) [user 2026-10-18 "Brennan = yes"; 2026-10-21 CAD records "following my rule"]</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>6835-06-06-06-NWO-FG</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
         </is>
@@ -535,32 +649,64 @@
           <t>6835-08-08-08-NWO-FG</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>6835-08-08-08-NWO-FG</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAT 2026-10-21: M7@DRIVE, M1@DRIVE, M2@DRIVE, D1@BORE, CHEX@HEX, Y@HEX] Brennan TFA catalog TFA-p061-t02 (CAD record agrees within the print rounding); port drill PD2@BORE, PD3@BORE = Air-Way per-size (A11) [user 2026-10-18 "Brennan = yes"; 2026-10-21 CAD records "following my rule"]</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>6835-08-08-08-NWO-FG</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
         </is>
@@ -572,32 +718,64 @@
           <t>6835-12-12-12-NWO-FG</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>6835-12-12-12-NWO-FG</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAT 2026-10-21: M7@DRIVE, M1@DRIVE, M2@DRIVE, D1@BORE, CHEX@HEX, Y@HEX] Brennan TFA catalog TFA-p061-t02 (CAD record agrees within the print rounding); port drill PD2@BORE, PD3@BORE = Air-Way per-size (A11) [user 2026-10-18 "Brennan = yes"; 2026-10-21 CAD records "following my rule"]</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>6835-12-12-12-NWO-FG</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
         </is>
